--- a/templates/計画申請/03_対象者一覧(様式第3-2号)_定額制.xlsx
+++ b/templates/計画申請/03_対象者一覧(様式第3-2号)_定額制.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr filterPrivacy="1"/>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49A2D3E0-B8EF-4233-87F9-AB2672631F08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="22276" windowHeight="13276" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="様式第3-2号" sheetId="10" r:id="rId1"/>
@@ -1153,6 +1153,43 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="3" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="13" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection locked="0"/>
@@ -1161,48 +1198,56 @@
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="10" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="11" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="12" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="2" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="9" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
@@ -1246,53 +1291,8 @@
       <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="2" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="9" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="3" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="13" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="10" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="11" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="12" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -1590,20 +1590,20 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:O80"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.6328125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="32.26953125" style="2" customWidth="1"/>
-    <col min="3" max="10" width="8.36328125" style="2" customWidth="1"/>
-    <col min="11" max="11" width="2.08984375" style="2" customWidth="1"/>
+    <col min="1" max="1" width="6.59765625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="32.265625" style="2" customWidth="1"/>
+    <col min="3" max="10" width="8.33203125" style="2" customWidth="1"/>
+    <col min="11" max="11" width="2.06640625" style="2" customWidth="1"/>
     <col min="12" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="48" t="s">
+    <row r="1" spans="1:15" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="61" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="48"/>
+      <c r="B1" s="61"/>
       <c r="C1" s="3"/>
       <c r="D1" s="3"/>
       <c r="E1" s="3"/>
@@ -1613,7 +1613,7 @@
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
     </row>
-    <row r="2" spans="1:15" s="1" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:15" s="1" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -1630,7 +1630,7 @@
       <c r="N2" s="3"/>
       <c r="O2" s="3"/>
     </row>
-    <row r="3" spans="1:15" s="1" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:15" s="1" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="8"/>
       <c r="B3" s="8"/>
       <c r="C3" s="8"/>
@@ -1650,7 +1650,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:15" s="1" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:15" s="1" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
@@ -1662,21 +1662,21 @@
       <c r="I4" s="3"/>
       <c r="J4" s="3"/>
     </row>
-    <row r="5" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="49" t="s">
+    <row r="5" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="62" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="49"/>
-      <c r="C5" s="49"/>
-      <c r="D5" s="49"/>
-      <c r="E5" s="49"/>
-      <c r="F5" s="49"/>
-      <c r="G5" s="49"/>
-      <c r="H5" s="49"/>
-      <c r="I5" s="49"/>
-      <c r="J5" s="49"/>
-    </row>
-    <row r="6" spans="1:15" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B5" s="62"/>
+      <c r="C5" s="62"/>
+      <c r="D5" s="62"/>
+      <c r="E5" s="62"/>
+      <c r="F5" s="62"/>
+      <c r="G5" s="62"/>
+      <c r="H5" s="62"/>
+      <c r="I5" s="62"/>
+      <c r="J5" s="62"/>
+    </row>
+    <row r="6" spans="1:15" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5"/>
       <c r="B6" s="5"/>
       <c r="C6" s="5"/>
@@ -1688,21 +1688,21 @@
       <c r="I6" s="5"/>
       <c r="J6" s="5"/>
     </row>
-    <row r="7" spans="1:15" ht="35.15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="50" t="s">
+    <row r="7" spans="1:15" ht="35.200000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="63" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="50"/>
-      <c r="C7" s="50"/>
-      <c r="D7" s="50"/>
-      <c r="E7" s="50"/>
-      <c r="F7" s="50"/>
-      <c r="G7" s="50"/>
-      <c r="H7" s="50"/>
-      <c r="I7" s="50"/>
-      <c r="J7" s="50"/>
-    </row>
-    <row r="8" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B7" s="63"/>
+      <c r="C7" s="63"/>
+      <c r="D7" s="63"/>
+      <c r="E7" s="63"/>
+      <c r="F7" s="63"/>
+      <c r="G7" s="63"/>
+      <c r="H7" s="63"/>
+      <c r="I7" s="63"/>
+      <c r="J7" s="63"/>
+    </row>
+    <row r="8" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="22"/>
       <c r="B8" s="22"/>
       <c r="C8" s="22"/>
@@ -1720,21 +1720,21 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="36" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:15" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="22"/>
       <c r="B9" s="22"/>
-      <c r="C9" s="57" t="s">
+      <c r="C9" s="70" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="57"/>
-      <c r="E9" s="58"/>
-      <c r="F9" s="58"/>
-      <c r="G9" s="58"/>
-      <c r="H9" s="58"/>
-      <c r="I9" s="58"/>
-      <c r="J9" s="58"/>
-    </row>
-    <row r="10" spans="1:15" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="D9" s="70"/>
+      <c r="E9" s="71"/>
+      <c r="F9" s="71"/>
+      <c r="G9" s="71"/>
+      <c r="H9" s="71"/>
+      <c r="I9" s="71"/>
+      <c r="J9" s="71"/>
+    </row>
+    <row r="10" spans="1:15" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="22"/>
       <c r="B10" s="22"/>
       <c r="C10" s="22"/>
@@ -1746,369 +1746,369 @@
       <c r="I10" s="22"/>
       <c r="J10" s="22"/>
     </row>
-    <row r="11" spans="1:15" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:15" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="15">
         <v>1</v>
       </c>
       <c r="B11" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="C11" s="51"/>
-      <c r="D11" s="52"/>
-      <c r="E11" s="52"/>
-      <c r="F11" s="52"/>
-      <c r="G11" s="52"/>
-      <c r="H11" s="52"/>
-      <c r="I11" s="52"/>
-      <c r="J11" s="53"/>
-    </row>
-    <row r="12" spans="1:15" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C11" s="64"/>
+      <c r="D11" s="65"/>
+      <c r="E11" s="65"/>
+      <c r="F11" s="65"/>
+      <c r="G11" s="65"/>
+      <c r="H11" s="65"/>
+      <c r="I11" s="65"/>
+      <c r="J11" s="66"/>
+    </row>
+    <row r="12" spans="1:15" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="17">
         <v>2</v>
       </c>
       <c r="B12" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="C12" s="54"/>
-      <c r="D12" s="55"/>
-      <c r="E12" s="55"/>
-      <c r="F12" s="55"/>
-      <c r="G12" s="55"/>
-      <c r="H12" s="55"/>
-      <c r="I12" s="55"/>
-      <c r="J12" s="56"/>
-    </row>
-    <row r="13" spans="1:15" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C12" s="67"/>
+      <c r="D12" s="68"/>
+      <c r="E12" s="68"/>
+      <c r="F12" s="68"/>
+      <c r="G12" s="68"/>
+      <c r="H12" s="68"/>
+      <c r="I12" s="68"/>
+      <c r="J12" s="69"/>
+    </row>
+    <row r="13" spans="1:15" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="17">
         <v>3</v>
       </c>
-      <c r="B13" s="59" t="s">
+      <c r="B13" s="53" t="s">
         <v>12</v>
       </c>
-      <c r="C13" s="59"/>
-      <c r="D13" s="59"/>
-      <c r="E13" s="59"/>
-      <c r="F13" s="59"/>
-      <c r="G13" s="59"/>
-      <c r="H13" s="59"/>
-      <c r="I13" s="59"/>
-      <c r="J13" s="60"/>
-    </row>
-    <row r="14" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="61" t="s">
+      <c r="C13" s="53"/>
+      <c r="D13" s="53"/>
+      <c r="E13" s="53"/>
+      <c r="F13" s="53"/>
+      <c r="G13" s="53"/>
+      <c r="H13" s="53"/>
+      <c r="I13" s="53"/>
+      <c r="J13" s="54"/>
+    </row>
+    <row r="14" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="42" t="s">
         <v>5</v>
       </c>
-      <c r="B14" s="62" t="s">
+      <c r="B14" s="37" t="s">
         <v>17</v>
       </c>
-      <c r="C14" s="63" t="s">
+      <c r="C14" s="47" t="s">
         <v>15</v>
       </c>
-      <c r="D14" s="64"/>
-      <c r="E14" s="64"/>
-      <c r="F14" s="64"/>
-      <c r="G14" s="64"/>
-      <c r="H14" s="64"/>
-      <c r="I14" s="64"/>
-      <c r="J14" s="65"/>
-    </row>
-    <row r="15" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="61"/>
-      <c r="B15" s="62"/>
-      <c r="C15" s="43" t="s">
+      <c r="D14" s="48"/>
+      <c r="E14" s="48"/>
+      <c r="F14" s="48"/>
+      <c r="G14" s="48"/>
+      <c r="H14" s="48"/>
+      <c r="I14" s="48"/>
+      <c r="J14" s="49"/>
+    </row>
+    <row r="15" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="42"/>
+      <c r="B15" s="37"/>
+      <c r="C15" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="D15" s="44"/>
-      <c r="E15" s="44"/>
-      <c r="F15" s="46"/>
-      <c r="G15" s="43" t="s">
+      <c r="D15" s="56"/>
+      <c r="E15" s="56"/>
+      <c r="F15" s="57"/>
+      <c r="G15" s="55" t="s">
         <v>7</v>
       </c>
-      <c r="H15" s="44"/>
-      <c r="I15" s="44"/>
-      <c r="J15" s="45"/>
-    </row>
-    <row r="16" spans="1:15" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H15" s="56"/>
+      <c r="I15" s="56"/>
+      <c r="J15" s="58"/>
+    </row>
+    <row r="16" spans="1:15" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="19">
         <v>1</v>
       </c>
       <c r="B16" s="29"/>
-      <c r="C16" s="37"/>
-      <c r="D16" s="38"/>
-      <c r="E16" s="38"/>
-      <c r="F16" s="39"/>
-      <c r="G16" s="37"/>
-      <c r="H16" s="38"/>
-      <c r="I16" s="38"/>
-      <c r="J16" s="40"/>
-    </row>
-    <row r="17" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C16" s="33"/>
+      <c r="D16" s="34"/>
+      <c r="E16" s="34"/>
+      <c r="F16" s="35"/>
+      <c r="G16" s="33"/>
+      <c r="H16" s="34"/>
+      <c r="I16" s="34"/>
+      <c r="J16" s="36"/>
+    </row>
+    <row r="17" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="19">
         <v>2</v>
       </c>
       <c r="B17" s="29"/>
-      <c r="C17" s="37"/>
-      <c r="D17" s="38"/>
-      <c r="E17" s="38"/>
-      <c r="F17" s="39"/>
-      <c r="G17" s="37"/>
-      <c r="H17" s="38"/>
-      <c r="I17" s="38"/>
-      <c r="J17" s="40"/>
-    </row>
-    <row r="18" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C17" s="33"/>
+      <c r="D17" s="34"/>
+      <c r="E17" s="34"/>
+      <c r="F17" s="35"/>
+      <c r="G17" s="33"/>
+      <c r="H17" s="34"/>
+      <c r="I17" s="34"/>
+      <c r="J17" s="36"/>
+    </row>
+    <row r="18" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="19">
         <v>3</v>
       </c>
       <c r="B18" s="29"/>
-      <c r="C18" s="37"/>
-      <c r="D18" s="38"/>
-      <c r="E18" s="38"/>
-      <c r="F18" s="39"/>
-      <c r="G18" s="37"/>
-      <c r="H18" s="38"/>
-      <c r="I18" s="38"/>
-      <c r="J18" s="40"/>
-    </row>
-    <row r="19" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C18" s="33"/>
+      <c r="D18" s="34"/>
+      <c r="E18" s="34"/>
+      <c r="F18" s="35"/>
+      <c r="G18" s="33"/>
+      <c r="H18" s="34"/>
+      <c r="I18" s="34"/>
+      <c r="J18" s="36"/>
+    </row>
+    <row r="19" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="19">
         <v>4</v>
       </c>
       <c r="B19" s="29"/>
-      <c r="C19" s="37"/>
-      <c r="D19" s="38"/>
-      <c r="E19" s="38"/>
-      <c r="F19" s="39"/>
-      <c r="G19" s="37"/>
-      <c r="H19" s="38"/>
-      <c r="I19" s="38"/>
-      <c r="J19" s="40"/>
-    </row>
-    <row r="20" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C19" s="33"/>
+      <c r="D19" s="34"/>
+      <c r="E19" s="34"/>
+      <c r="F19" s="35"/>
+      <c r="G19" s="33"/>
+      <c r="H19" s="34"/>
+      <c r="I19" s="34"/>
+      <c r="J19" s="36"/>
+    </row>
+    <row r="20" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="19">
         <v>5</v>
       </c>
       <c r="B20" s="29"/>
-      <c r="C20" s="37"/>
-      <c r="D20" s="38"/>
-      <c r="E20" s="38"/>
-      <c r="F20" s="39"/>
-      <c r="G20" s="37"/>
-      <c r="H20" s="38"/>
-      <c r="I20" s="38"/>
-      <c r="J20" s="40"/>
-    </row>
-    <row r="21" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C20" s="33"/>
+      <c r="D20" s="34"/>
+      <c r="E20" s="34"/>
+      <c r="F20" s="35"/>
+      <c r="G20" s="33"/>
+      <c r="H20" s="34"/>
+      <c r="I20" s="34"/>
+      <c r="J20" s="36"/>
+    </row>
+    <row r="21" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="19">
         <v>6</v>
       </c>
       <c r="B21" s="29"/>
-      <c r="C21" s="37"/>
-      <c r="D21" s="38"/>
-      <c r="E21" s="38"/>
-      <c r="F21" s="39"/>
-      <c r="G21" s="37"/>
-      <c r="H21" s="38"/>
-      <c r="I21" s="38"/>
-      <c r="J21" s="40"/>
-    </row>
-    <row r="22" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C21" s="33"/>
+      <c r="D21" s="34"/>
+      <c r="E21" s="34"/>
+      <c r="F21" s="35"/>
+      <c r="G21" s="33"/>
+      <c r="H21" s="34"/>
+      <c r="I21" s="34"/>
+      <c r="J21" s="36"/>
+    </row>
+    <row r="22" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="19">
         <v>7</v>
       </c>
       <c r="B22" s="29"/>
-      <c r="C22" s="37"/>
-      <c r="D22" s="38"/>
-      <c r="E22" s="38"/>
-      <c r="F22" s="39"/>
-      <c r="G22" s="37"/>
-      <c r="H22" s="38"/>
-      <c r="I22" s="38"/>
-      <c r="J22" s="40"/>
-    </row>
-    <row r="23" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C22" s="33"/>
+      <c r="D22" s="34"/>
+      <c r="E22" s="34"/>
+      <c r="F22" s="35"/>
+      <c r="G22" s="33"/>
+      <c r="H22" s="34"/>
+      <c r="I22" s="34"/>
+      <c r="J22" s="36"/>
+    </row>
+    <row r="23" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="19">
         <v>8</v>
       </c>
       <c r="B23" s="29"/>
-      <c r="C23" s="37"/>
-      <c r="D23" s="38"/>
-      <c r="E23" s="38"/>
-      <c r="F23" s="39"/>
-      <c r="G23" s="37"/>
-      <c r="H23" s="38"/>
-      <c r="I23" s="38"/>
-      <c r="J23" s="40"/>
-    </row>
-    <row r="24" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C23" s="33"/>
+      <c r="D23" s="34"/>
+      <c r="E23" s="34"/>
+      <c r="F23" s="35"/>
+      <c r="G23" s="33"/>
+      <c r="H23" s="34"/>
+      <c r="I23" s="34"/>
+      <c r="J23" s="36"/>
+    </row>
+    <row r="24" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="19">
         <v>9</v>
       </c>
       <c r="B24" s="29"/>
-      <c r="C24" s="37"/>
-      <c r="D24" s="38"/>
-      <c r="E24" s="38"/>
-      <c r="F24" s="39"/>
-      <c r="G24" s="37"/>
-      <c r="H24" s="38"/>
-      <c r="I24" s="38"/>
-      <c r="J24" s="40"/>
-    </row>
-    <row r="25" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C24" s="33"/>
+      <c r="D24" s="34"/>
+      <c r="E24" s="34"/>
+      <c r="F24" s="35"/>
+      <c r="G24" s="33"/>
+      <c r="H24" s="34"/>
+      <c r="I24" s="34"/>
+      <c r="J24" s="36"/>
+    </row>
+    <row r="25" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="19">
         <v>10</v>
       </c>
       <c r="B25" s="29"/>
-      <c r="C25" s="37"/>
-      <c r="D25" s="38"/>
-      <c r="E25" s="38"/>
-      <c r="F25" s="39"/>
-      <c r="G25" s="37"/>
-      <c r="H25" s="38"/>
-      <c r="I25" s="38"/>
-      <c r="J25" s="40"/>
-    </row>
-    <row r="26" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C25" s="33"/>
+      <c r="D25" s="34"/>
+      <c r="E25" s="34"/>
+      <c r="F25" s="35"/>
+      <c r="G25" s="33"/>
+      <c r="H25" s="34"/>
+      <c r="I25" s="34"/>
+      <c r="J25" s="36"/>
+    </row>
+    <row r="26" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="19">
         <v>11</v>
       </c>
       <c r="B26" s="29"/>
-      <c r="C26" s="37"/>
-      <c r="D26" s="38"/>
-      <c r="E26" s="38"/>
-      <c r="F26" s="39"/>
-      <c r="G26" s="37"/>
-      <c r="H26" s="38"/>
-      <c r="I26" s="38"/>
-      <c r="J26" s="40"/>
-    </row>
-    <row r="27" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C26" s="33"/>
+      <c r="D26" s="34"/>
+      <c r="E26" s="34"/>
+      <c r="F26" s="35"/>
+      <c r="G26" s="33"/>
+      <c r="H26" s="34"/>
+      <c r="I26" s="34"/>
+      <c r="J26" s="36"/>
+    </row>
+    <row r="27" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="19">
         <v>12</v>
       </c>
       <c r="B27" s="29"/>
-      <c r="C27" s="37"/>
-      <c r="D27" s="38"/>
-      <c r="E27" s="38"/>
-      <c r="F27" s="39"/>
-      <c r="G27" s="37"/>
-      <c r="H27" s="38"/>
-      <c r="I27" s="38"/>
-      <c r="J27" s="40"/>
-    </row>
-    <row r="28" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C27" s="33"/>
+      <c r="D27" s="34"/>
+      <c r="E27" s="34"/>
+      <c r="F27" s="35"/>
+      <c r="G27" s="33"/>
+      <c r="H27" s="34"/>
+      <c r="I27" s="34"/>
+      <c r="J27" s="36"/>
+    </row>
+    <row r="28" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="19">
         <v>13</v>
       </c>
       <c r="B28" s="29"/>
-      <c r="C28" s="37"/>
-      <c r="D28" s="38"/>
-      <c r="E28" s="38"/>
-      <c r="F28" s="39"/>
-      <c r="G28" s="37"/>
-      <c r="H28" s="38"/>
-      <c r="I28" s="38"/>
-      <c r="J28" s="40"/>
-    </row>
-    <row r="29" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C28" s="33"/>
+      <c r="D28" s="34"/>
+      <c r="E28" s="34"/>
+      <c r="F28" s="35"/>
+      <c r="G28" s="33"/>
+      <c r="H28" s="34"/>
+      <c r="I28" s="34"/>
+      <c r="J28" s="36"/>
+    </row>
+    <row r="29" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="19">
         <v>14</v>
       </c>
       <c r="B29" s="29"/>
-      <c r="C29" s="37"/>
-      <c r="D29" s="38"/>
-      <c r="E29" s="38"/>
-      <c r="F29" s="39"/>
-      <c r="G29" s="37"/>
-      <c r="H29" s="38"/>
-      <c r="I29" s="38"/>
-      <c r="J29" s="40"/>
-    </row>
-    <row r="30" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C29" s="33"/>
+      <c r="D29" s="34"/>
+      <c r="E29" s="34"/>
+      <c r="F29" s="35"/>
+      <c r="G29" s="33"/>
+      <c r="H29" s="34"/>
+      <c r="I29" s="34"/>
+      <c r="J29" s="36"/>
+    </row>
+    <row r="30" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="19">
         <v>15</v>
       </c>
       <c r="B30" s="29"/>
-      <c r="C30" s="37"/>
-      <c r="D30" s="38"/>
-      <c r="E30" s="38"/>
-      <c r="F30" s="39"/>
-      <c r="G30" s="37"/>
-      <c r="H30" s="38"/>
-      <c r="I30" s="38"/>
-      <c r="J30" s="40"/>
-    </row>
-    <row r="31" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C30" s="33"/>
+      <c r="D30" s="34"/>
+      <c r="E30" s="34"/>
+      <c r="F30" s="35"/>
+      <c r="G30" s="33"/>
+      <c r="H30" s="34"/>
+      <c r="I30" s="34"/>
+      <c r="J30" s="36"/>
+    </row>
+    <row r="31" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="19">
         <v>16</v>
       </c>
       <c r="B31" s="29"/>
-      <c r="C31" s="37"/>
-      <c r="D31" s="38"/>
-      <c r="E31" s="38"/>
-      <c r="F31" s="39"/>
-      <c r="G31" s="37"/>
-      <c r="H31" s="38"/>
-      <c r="I31" s="38"/>
-      <c r="J31" s="40"/>
-    </row>
-    <row r="32" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C31" s="33"/>
+      <c r="D31" s="34"/>
+      <c r="E31" s="34"/>
+      <c r="F31" s="35"/>
+      <c r="G31" s="33"/>
+      <c r="H31" s="34"/>
+      <c r="I31" s="34"/>
+      <c r="J31" s="36"/>
+    </row>
+    <row r="32" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="19">
         <v>17</v>
       </c>
       <c r="B32" s="29"/>
-      <c r="C32" s="37"/>
-      <c r="D32" s="38"/>
-      <c r="E32" s="38"/>
-      <c r="F32" s="39"/>
-      <c r="G32" s="37"/>
-      <c r="H32" s="38"/>
-      <c r="I32" s="38"/>
-      <c r="J32" s="40"/>
-    </row>
-    <row r="33" spans="1:15" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C32" s="33"/>
+      <c r="D32" s="34"/>
+      <c r="E32" s="34"/>
+      <c r="F32" s="35"/>
+      <c r="G32" s="33"/>
+      <c r="H32" s="34"/>
+      <c r="I32" s="34"/>
+      <c r="J32" s="36"/>
+    </row>
+    <row r="33" spans="1:15" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="19">
         <v>18</v>
       </c>
       <c r="B33" s="29"/>
-      <c r="C33" s="37"/>
-      <c r="D33" s="38"/>
-      <c r="E33" s="38"/>
-      <c r="F33" s="39"/>
-      <c r="G33" s="37"/>
-      <c r="H33" s="38"/>
-      <c r="I33" s="38"/>
-      <c r="J33" s="40"/>
-    </row>
-    <row r="34" spans="1:15" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C33" s="33"/>
+      <c r="D33" s="34"/>
+      <c r="E33" s="34"/>
+      <c r="F33" s="35"/>
+      <c r="G33" s="33"/>
+      <c r="H33" s="34"/>
+      <c r="I33" s="34"/>
+      <c r="J33" s="36"/>
+    </row>
+    <row r="34" spans="1:15" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="19">
         <v>19</v>
       </c>
       <c r="B34" s="29"/>
-      <c r="C34" s="37"/>
-      <c r="D34" s="38"/>
-      <c r="E34" s="38"/>
-      <c r="F34" s="39"/>
-      <c r="G34" s="37"/>
-      <c r="H34" s="38"/>
-      <c r="I34" s="38"/>
-      <c r="J34" s="40"/>
-    </row>
-    <row r="35" spans="1:15" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C34" s="33"/>
+      <c r="D34" s="34"/>
+      <c r="E34" s="34"/>
+      <c r="F34" s="35"/>
+      <c r="G34" s="33"/>
+      <c r="H34" s="34"/>
+      <c r="I34" s="34"/>
+      <c r="J34" s="36"/>
+    </row>
+    <row r="35" spans="1:15" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="20">
         <v>20</v>
       </c>
       <c r="B35" s="30"/>
-      <c r="C35" s="33"/>
-      <c r="D35" s="34"/>
-      <c r="E35" s="34"/>
-      <c r="F35" s="35"/>
-      <c r="G35" s="33"/>
-      <c r="H35" s="34"/>
-      <c r="I35" s="34"/>
-      <c r="J35" s="36"/>
-    </row>
-    <row r="36" spans="1:15" s="1" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C35" s="43"/>
+      <c r="D35" s="44"/>
+      <c r="E35" s="44"/>
+      <c r="F35" s="59"/>
+      <c r="G35" s="43"/>
+      <c r="H35" s="44"/>
+      <c r="I35" s="44"/>
+      <c r="J35" s="45"/>
+    </row>
+    <row r="36" spans="1:15" s="1" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="6"/>
       <c r="B36" s="6"/>
       <c r="C36" s="6"/>
@@ -2120,11 +2120,11 @@
       <c r="I36" s="6"/>
       <c r="J36" s="6"/>
     </row>
-    <row r="37" spans="1:15" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="69" t="s">
+    <row r="37" spans="1:15" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="41" t="s">
         <v>8</v>
       </c>
-      <c r="B37" s="69"/>
+      <c r="B37" s="41"/>
       <c r="C37" s="24"/>
       <c r="D37" s="24"/>
       <c r="E37" s="24"/>
@@ -2134,107 +2134,107 @@
       <c r="I37" s="13"/>
       <c r="J37" s="14"/>
     </row>
-    <row r="38" spans="1:15" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:15" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="25">
         <v>1</v>
       </c>
-      <c r="B38" s="41" t="s">
+      <c r="B38" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="C38" s="41"/>
-      <c r="D38" s="41"/>
-      <c r="E38" s="41"/>
-      <c r="F38" s="41"/>
-      <c r="G38" s="41"/>
-      <c r="H38" s="41"/>
-      <c r="I38" s="41"/>
-      <c r="J38" s="41"/>
-    </row>
-    <row r="39" spans="1:15" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C38" s="46"/>
+      <c r="D38" s="46"/>
+      <c r="E38" s="46"/>
+      <c r="F38" s="46"/>
+      <c r="G38" s="46"/>
+      <c r="H38" s="46"/>
+      <c r="I38" s="46"/>
+      <c r="J38" s="46"/>
+    </row>
+    <row r="39" spans="1:15" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="25">
         <v>2</v>
       </c>
-      <c r="B39" s="42" t="s">
+      <c r="B39" s="72" t="s">
         <v>18</v>
       </c>
-      <c r="C39" s="42"/>
-      <c r="D39" s="42"/>
-      <c r="E39" s="42"/>
-      <c r="F39" s="42"/>
-      <c r="G39" s="42"/>
-      <c r="H39" s="42"/>
-      <c r="I39" s="42"/>
+      <c r="C39" s="72"/>
+      <c r="D39" s="72"/>
+      <c r="E39" s="72"/>
+      <c r="F39" s="72"/>
+      <c r="G39" s="72"/>
+      <c r="H39" s="72"/>
+      <c r="I39" s="72"/>
       <c r="J39" s="14"/>
     </row>
-    <row r="40" spans="1:15" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:15" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="25">
         <v>3</v>
       </c>
-      <c r="B40" s="42" t="s">
+      <c r="B40" s="72" t="s">
         <v>24</v>
       </c>
-      <c r="C40" s="42"/>
-      <c r="D40" s="42"/>
-      <c r="E40" s="42"/>
-      <c r="F40" s="42"/>
-      <c r="G40" s="42"/>
-      <c r="H40" s="42"/>
-      <c r="I40" s="42"/>
+      <c r="C40" s="72"/>
+      <c r="D40" s="72"/>
+      <c r="E40" s="72"/>
+      <c r="F40" s="72"/>
+      <c r="G40" s="72"/>
+      <c r="H40" s="72"/>
+      <c r="I40" s="72"/>
       <c r="J40" s="14"/>
     </row>
-    <row r="41" spans="1:15" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:15" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="25">
         <v>4</v>
       </c>
-      <c r="B41" s="41" t="s">
+      <c r="B41" s="46" t="s">
         <v>19</v>
       </c>
-      <c r="C41" s="41"/>
-      <c r="D41" s="41"/>
-      <c r="E41" s="41"/>
-      <c r="F41" s="41"/>
-      <c r="G41" s="41"/>
-      <c r="H41" s="41"/>
-      <c r="I41" s="41"/>
-      <c r="J41" s="41"/>
-    </row>
-    <row r="42" spans="1:15" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C41" s="46"/>
+      <c r="D41" s="46"/>
+      <c r="E41" s="46"/>
+      <c r="F41" s="46"/>
+      <c r="G41" s="46"/>
+      <c r="H41" s="46"/>
+      <c r="I41" s="46"/>
+      <c r="J41" s="46"/>
+    </row>
+    <row r="42" spans="1:15" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="25">
         <v>5</v>
       </c>
-      <c r="B42" s="41" t="s">
+      <c r="B42" s="46" t="s">
         <v>25</v>
       </c>
-      <c r="C42" s="41"/>
-      <c r="D42" s="41"/>
-      <c r="E42" s="41"/>
-      <c r="F42" s="41"/>
-      <c r="G42" s="41"/>
-      <c r="H42" s="41"/>
-      <c r="I42" s="41"/>
+      <c r="C42" s="46"/>
+      <c r="D42" s="46"/>
+      <c r="E42" s="46"/>
+      <c r="F42" s="46"/>
+      <c r="G42" s="46"/>
+      <c r="H42" s="46"/>
+      <c r="I42" s="46"/>
       <c r="J42" s="14"/>
     </row>
-    <row r="43" spans="1:15" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:15" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="25">
         <v>6</v>
       </c>
-      <c r="B43" s="41" t="s">
+      <c r="B43" s="46" t="s">
         <v>10</v>
       </c>
-      <c r="C43" s="41"/>
-      <c r="D43" s="41"/>
-      <c r="E43" s="41"/>
-      <c r="F43" s="41"/>
-      <c r="G43" s="41"/>
-      <c r="H43" s="41"/>
-      <c r="I43" s="41"/>
-      <c r="J43" s="41"/>
-    </row>
-    <row r="44" spans="1:15" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="47" t="s">
+      <c r="C43" s="46"/>
+      <c r="D43" s="46"/>
+      <c r="E43" s="46"/>
+      <c r="F43" s="46"/>
+      <c r="G43" s="46"/>
+      <c r="H43" s="46"/>
+      <c r="I43" s="46"/>
+      <c r="J43" s="46"/>
+    </row>
+    <row r="44" spans="1:15" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="60" t="s">
         <v>23</v>
       </c>
-      <c r="B44" s="47"/>
+      <c r="B44" s="60"/>
       <c r="C44" s="3"/>
       <c r="D44" s="3"/>
       <c r="E44" s="3"/>
@@ -2244,7 +2244,7 @@
       <c r="I44" s="3"/>
       <c r="J44" s="3"/>
     </row>
-    <row r="45" spans="1:15" s="1" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:15" s="1" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="3"/>
       <c r="B45" s="3"/>
       <c r="C45" s="3"/>
@@ -2261,7 +2261,7 @@
       <c r="N45" s="3"/>
       <c r="O45" s="3"/>
     </row>
-    <row r="46" spans="1:15" s="1" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:15" s="1" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="8"/>
       <c r="B46" s="8"/>
       <c r="C46" s="8"/>
@@ -2281,7 +2281,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="47" spans="1:15" s="1" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:15" s="1" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="3"/>
       <c r="B47" s="3"/>
       <c r="C47" s="3"/>
@@ -2293,21 +2293,21 @@
       <c r="I47" s="3"/>
       <c r="J47" s="3"/>
     </row>
-    <row r="48" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="49" t="s">
+    <row r="48" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="62" t="s">
         <v>20</v>
       </c>
-      <c r="B48" s="49"/>
-      <c r="C48" s="49"/>
-      <c r="D48" s="49"/>
-      <c r="E48" s="49"/>
-      <c r="F48" s="49"/>
-      <c r="G48" s="49"/>
-      <c r="H48" s="49"/>
-      <c r="I48" s="49"/>
-      <c r="J48" s="49"/>
-    </row>
-    <row r="49" spans="1:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B48" s="62"/>
+      <c r="C48" s="62"/>
+      <c r="D48" s="62"/>
+      <c r="E48" s="62"/>
+      <c r="F48" s="62"/>
+      <c r="G48" s="62"/>
+      <c r="H48" s="62"/>
+      <c r="I48" s="62"/>
+      <c r="J48" s="62"/>
+    </row>
+    <row r="49" spans="1:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="21"/>
       <c r="B49" s="21"/>
       <c r="C49" s="21"/>
@@ -2319,389 +2319,389 @@
       <c r="I49" s="21"/>
       <c r="J49" s="21"/>
     </row>
-    <row r="50" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="15">
         <v>1</v>
       </c>
       <c r="B50" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="C50" s="70"/>
-      <c r="D50" s="71"/>
-      <c r="E50" s="71"/>
-      <c r="F50" s="71"/>
-      <c r="G50" s="71"/>
-      <c r="H50" s="71"/>
-      <c r="I50" s="71"/>
-      <c r="J50" s="72"/>
-    </row>
-    <row r="51" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C50" s="50"/>
+      <c r="D50" s="51"/>
+      <c r="E50" s="51"/>
+      <c r="F50" s="51"/>
+      <c r="G50" s="51"/>
+      <c r="H50" s="51"/>
+      <c r="I50" s="51"/>
+      <c r="J50" s="52"/>
+    </row>
+    <row r="51" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="17">
         <v>2</v>
       </c>
       <c r="B51" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="C51" s="66"/>
-      <c r="D51" s="67"/>
-      <c r="E51" s="67"/>
-      <c r="F51" s="67"/>
-      <c r="G51" s="67"/>
-      <c r="H51" s="67"/>
-      <c r="I51" s="67"/>
-      <c r="J51" s="68"/>
-    </row>
-    <row r="52" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C51" s="38"/>
+      <c r="D51" s="39"/>
+      <c r="E51" s="39"/>
+      <c r="F51" s="39"/>
+      <c r="G51" s="39"/>
+      <c r="H51" s="39"/>
+      <c r="I51" s="39"/>
+      <c r="J51" s="40"/>
+    </row>
+    <row r="52" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="17">
         <v>3</v>
       </c>
-      <c r="B52" s="59" t="s">
+      <c r="B52" s="53" t="s">
         <v>12</v>
       </c>
-      <c r="C52" s="59"/>
-      <c r="D52" s="59"/>
-      <c r="E52" s="59"/>
-      <c r="F52" s="59"/>
-      <c r="G52" s="59"/>
-      <c r="H52" s="59"/>
-      <c r="I52" s="59"/>
-      <c r="J52" s="60"/>
-    </row>
-    <row r="53" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="61" t="s">
+      <c r="C52" s="53"/>
+      <c r="D52" s="53"/>
+      <c r="E52" s="53"/>
+      <c r="F52" s="53"/>
+      <c r="G52" s="53"/>
+      <c r="H52" s="53"/>
+      <c r="I52" s="53"/>
+      <c r="J52" s="54"/>
+    </row>
+    <row r="53" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="42" t="s">
         <v>5</v>
       </c>
-      <c r="B53" s="62" t="s">
+      <c r="B53" s="37" t="s">
         <v>17</v>
       </c>
-      <c r="C53" s="63" t="s">
+      <c r="C53" s="47" t="s">
         <v>15</v>
       </c>
-      <c r="D53" s="64"/>
-      <c r="E53" s="64"/>
-      <c r="F53" s="64"/>
-      <c r="G53" s="64"/>
-      <c r="H53" s="64"/>
-      <c r="I53" s="64"/>
-      <c r="J53" s="65"/>
-    </row>
-    <row r="54" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="61"/>
-      <c r="B54" s="62"/>
-      <c r="C54" s="43" t="s">
+      <c r="D53" s="48"/>
+      <c r="E53" s="48"/>
+      <c r="F53" s="48"/>
+      <c r="G53" s="48"/>
+      <c r="H53" s="48"/>
+      <c r="I53" s="48"/>
+      <c r="J53" s="49"/>
+    </row>
+    <row r="54" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="42"/>
+      <c r="B54" s="37"/>
+      <c r="C54" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="D54" s="44"/>
-      <c r="E54" s="44"/>
-      <c r="F54" s="46"/>
-      <c r="G54" s="43" t="s">
+      <c r="D54" s="56"/>
+      <c r="E54" s="56"/>
+      <c r="F54" s="57"/>
+      <c r="G54" s="55" t="s">
         <v>7</v>
       </c>
-      <c r="H54" s="44"/>
-      <c r="I54" s="44"/>
-      <c r="J54" s="45"/>
-    </row>
-    <row r="55" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H54" s="56"/>
+      <c r="I54" s="56"/>
+      <c r="J54" s="58"/>
+    </row>
+    <row r="55" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="31"/>
       <c r="B55" s="29"/>
-      <c r="C55" s="37"/>
-      <c r="D55" s="38"/>
-      <c r="E55" s="38"/>
-      <c r="F55" s="39"/>
-      <c r="G55" s="37"/>
-      <c r="H55" s="38"/>
-      <c r="I55" s="38"/>
-      <c r="J55" s="40"/>
-    </row>
-    <row r="56" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C55" s="33"/>
+      <c r="D55" s="34"/>
+      <c r="E55" s="34"/>
+      <c r="F55" s="35"/>
+      <c r="G55" s="33"/>
+      <c r="H55" s="34"/>
+      <c r="I55" s="34"/>
+      <c r="J55" s="36"/>
+    </row>
+    <row r="56" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="31"/>
       <c r="B56" s="29"/>
-      <c r="C56" s="37"/>
-      <c r="D56" s="38"/>
-      <c r="E56" s="38"/>
-      <c r="F56" s="39"/>
-      <c r="G56" s="37"/>
-      <c r="H56" s="38"/>
-      <c r="I56" s="38"/>
-      <c r="J56" s="40"/>
-    </row>
-    <row r="57" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C56" s="33"/>
+      <c r="D56" s="34"/>
+      <c r="E56" s="34"/>
+      <c r="F56" s="35"/>
+      <c r="G56" s="33"/>
+      <c r="H56" s="34"/>
+      <c r="I56" s="34"/>
+      <c r="J56" s="36"/>
+    </row>
+    <row r="57" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="31"/>
       <c r="B57" s="29"/>
-      <c r="C57" s="37"/>
-      <c r="D57" s="38"/>
-      <c r="E57" s="38"/>
-      <c r="F57" s="39"/>
-      <c r="G57" s="37"/>
-      <c r="H57" s="38"/>
-      <c r="I57" s="38"/>
-      <c r="J57" s="40"/>
-    </row>
-    <row r="58" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C57" s="33"/>
+      <c r="D57" s="34"/>
+      <c r="E57" s="34"/>
+      <c r="F57" s="35"/>
+      <c r="G57" s="33"/>
+      <c r="H57" s="34"/>
+      <c r="I57" s="34"/>
+      <c r="J57" s="36"/>
+    </row>
+    <row r="58" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="31"/>
       <c r="B58" s="29"/>
-      <c r="C58" s="37"/>
-      <c r="D58" s="38"/>
-      <c r="E58" s="38"/>
-      <c r="F58" s="39"/>
-      <c r="G58" s="37"/>
-      <c r="H58" s="38"/>
-      <c r="I58" s="38"/>
-      <c r="J58" s="40"/>
-    </row>
-    <row r="59" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C58" s="33"/>
+      <c r="D58" s="34"/>
+      <c r="E58" s="34"/>
+      <c r="F58" s="35"/>
+      <c r="G58" s="33"/>
+      <c r="H58" s="34"/>
+      <c r="I58" s="34"/>
+      <c r="J58" s="36"/>
+    </row>
+    <row r="59" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="31"/>
       <c r="B59" s="29"/>
-      <c r="C59" s="37"/>
-      <c r="D59" s="38"/>
-      <c r="E59" s="38"/>
-      <c r="F59" s="39"/>
-      <c r="G59" s="37"/>
-      <c r="H59" s="38"/>
-      <c r="I59" s="38"/>
-      <c r="J59" s="40"/>
-    </row>
-    <row r="60" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C59" s="33"/>
+      <c r="D59" s="34"/>
+      <c r="E59" s="34"/>
+      <c r="F59" s="35"/>
+      <c r="G59" s="33"/>
+      <c r="H59" s="34"/>
+      <c r="I59" s="34"/>
+      <c r="J59" s="36"/>
+    </row>
+    <row r="60" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="31"/>
       <c r="B60" s="29"/>
-      <c r="C60" s="37"/>
-      <c r="D60" s="38"/>
-      <c r="E60" s="38"/>
-      <c r="F60" s="39"/>
-      <c r="G60" s="37"/>
-      <c r="H60" s="38"/>
-      <c r="I60" s="38"/>
-      <c r="J60" s="40"/>
-    </row>
-    <row r="61" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C60" s="33"/>
+      <c r="D60" s="34"/>
+      <c r="E60" s="34"/>
+      <c r="F60" s="35"/>
+      <c r="G60" s="33"/>
+      <c r="H60" s="34"/>
+      <c r="I60" s="34"/>
+      <c r="J60" s="36"/>
+    </row>
+    <row r="61" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="31"/>
       <c r="B61" s="29"/>
-      <c r="C61" s="37"/>
-      <c r="D61" s="38"/>
-      <c r="E61" s="38"/>
-      <c r="F61" s="39"/>
-      <c r="G61" s="37"/>
-      <c r="H61" s="38"/>
-      <c r="I61" s="38"/>
-      <c r="J61" s="40"/>
-    </row>
-    <row r="62" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C61" s="33"/>
+      <c r="D61" s="34"/>
+      <c r="E61" s="34"/>
+      <c r="F61" s="35"/>
+      <c r="G61" s="33"/>
+      <c r="H61" s="34"/>
+      <c r="I61" s="34"/>
+      <c r="J61" s="36"/>
+    </row>
+    <row r="62" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="31"/>
       <c r="B62" s="29"/>
-      <c r="C62" s="37"/>
-      <c r="D62" s="38"/>
-      <c r="E62" s="38"/>
-      <c r="F62" s="39"/>
-      <c r="G62" s="37"/>
-      <c r="H62" s="38"/>
-      <c r="I62" s="38"/>
-      <c r="J62" s="40"/>
-    </row>
-    <row r="63" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C62" s="33"/>
+      <c r="D62" s="34"/>
+      <c r="E62" s="34"/>
+      <c r="F62" s="35"/>
+      <c r="G62" s="33"/>
+      <c r="H62" s="34"/>
+      <c r="I62" s="34"/>
+      <c r="J62" s="36"/>
+    </row>
+    <row r="63" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="31"/>
       <c r="B63" s="29"/>
-      <c r="C63" s="37"/>
-      <c r="D63" s="38"/>
-      <c r="E63" s="38"/>
-      <c r="F63" s="39"/>
-      <c r="G63" s="37"/>
-      <c r="H63" s="38"/>
-      <c r="I63" s="38"/>
-      <c r="J63" s="40"/>
-    </row>
-    <row r="64" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C63" s="33"/>
+      <c r="D63" s="34"/>
+      <c r="E63" s="34"/>
+      <c r="F63" s="35"/>
+      <c r="G63" s="33"/>
+      <c r="H63" s="34"/>
+      <c r="I63" s="34"/>
+      <c r="J63" s="36"/>
+    </row>
+    <row r="64" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="31"/>
       <c r="B64" s="29"/>
-      <c r="C64" s="37"/>
-      <c r="D64" s="38"/>
-      <c r="E64" s="38"/>
-      <c r="F64" s="39"/>
-      <c r="G64" s="37"/>
-      <c r="H64" s="38"/>
-      <c r="I64" s="38"/>
-      <c r="J64" s="40"/>
-    </row>
-    <row r="65" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C64" s="33"/>
+      <c r="D64" s="34"/>
+      <c r="E64" s="34"/>
+      <c r="F64" s="35"/>
+      <c r="G64" s="33"/>
+      <c r="H64" s="34"/>
+      <c r="I64" s="34"/>
+      <c r="J64" s="36"/>
+    </row>
+    <row r="65" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="31"/>
       <c r="B65" s="29"/>
-      <c r="C65" s="37"/>
-      <c r="D65" s="38"/>
-      <c r="E65" s="38"/>
-      <c r="F65" s="39"/>
-      <c r="G65" s="37"/>
-      <c r="H65" s="38"/>
-      <c r="I65" s="38"/>
-      <c r="J65" s="40"/>
-    </row>
-    <row r="66" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C65" s="33"/>
+      <c r="D65" s="34"/>
+      <c r="E65" s="34"/>
+      <c r="F65" s="35"/>
+      <c r="G65" s="33"/>
+      <c r="H65" s="34"/>
+      <c r="I65" s="34"/>
+      <c r="J65" s="36"/>
+    </row>
+    <row r="66" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="31"/>
       <c r="B66" s="29"/>
-      <c r="C66" s="37"/>
-      <c r="D66" s="38"/>
-      <c r="E66" s="38"/>
-      <c r="F66" s="39"/>
-      <c r="G66" s="37"/>
-      <c r="H66" s="38"/>
-      <c r="I66" s="38"/>
-      <c r="J66" s="40"/>
-    </row>
-    <row r="67" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C66" s="33"/>
+      <c r="D66" s="34"/>
+      <c r="E66" s="34"/>
+      <c r="F66" s="35"/>
+      <c r="G66" s="33"/>
+      <c r="H66" s="34"/>
+      <c r="I66" s="34"/>
+      <c r="J66" s="36"/>
+    </row>
+    <row r="67" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="31"/>
       <c r="B67" s="29"/>
-      <c r="C67" s="37"/>
-      <c r="D67" s="38"/>
-      <c r="E67" s="38"/>
-      <c r="F67" s="39"/>
-      <c r="G67" s="37"/>
-      <c r="H67" s="38"/>
-      <c r="I67" s="38"/>
-      <c r="J67" s="40"/>
-    </row>
-    <row r="68" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C67" s="33"/>
+      <c r="D67" s="34"/>
+      <c r="E67" s="34"/>
+      <c r="F67" s="35"/>
+      <c r="G67" s="33"/>
+      <c r="H67" s="34"/>
+      <c r="I67" s="34"/>
+      <c r="J67" s="36"/>
+    </row>
+    <row r="68" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="31"/>
       <c r="B68" s="29"/>
-      <c r="C68" s="37"/>
-      <c r="D68" s="38"/>
-      <c r="E68" s="38"/>
-      <c r="F68" s="39"/>
-      <c r="G68" s="37"/>
-      <c r="H68" s="38"/>
-      <c r="I68" s="38"/>
-      <c r="J68" s="40"/>
-    </row>
-    <row r="69" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C68" s="33"/>
+      <c r="D68" s="34"/>
+      <c r="E68" s="34"/>
+      <c r="F68" s="35"/>
+      <c r="G68" s="33"/>
+      <c r="H68" s="34"/>
+      <c r="I68" s="34"/>
+      <c r="J68" s="36"/>
+    </row>
+    <row r="69" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="31"/>
       <c r="B69" s="29"/>
-      <c r="C69" s="37"/>
-      <c r="D69" s="38"/>
-      <c r="E69" s="38"/>
-      <c r="F69" s="39"/>
-      <c r="G69" s="37"/>
-      <c r="H69" s="38"/>
-      <c r="I69" s="38"/>
-      <c r="J69" s="40"/>
-    </row>
-    <row r="70" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C69" s="33"/>
+      <c r="D69" s="34"/>
+      <c r="E69" s="34"/>
+      <c r="F69" s="35"/>
+      <c r="G69" s="33"/>
+      <c r="H69" s="34"/>
+      <c r="I69" s="34"/>
+      <c r="J69" s="36"/>
+    </row>
+    <row r="70" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="31"/>
       <c r="B70" s="29"/>
-      <c r="C70" s="37"/>
-      <c r="D70" s="38"/>
-      <c r="E70" s="38"/>
-      <c r="F70" s="39"/>
-      <c r="G70" s="37"/>
-      <c r="H70" s="38"/>
-      <c r="I70" s="38"/>
-      <c r="J70" s="40"/>
-    </row>
-    <row r="71" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C70" s="33"/>
+      <c r="D70" s="34"/>
+      <c r="E70" s="34"/>
+      <c r="F70" s="35"/>
+      <c r="G70" s="33"/>
+      <c r="H70" s="34"/>
+      <c r="I70" s="34"/>
+      <c r="J70" s="36"/>
+    </row>
+    <row r="71" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="31"/>
       <c r="B71" s="29"/>
-      <c r="C71" s="37"/>
-      <c r="D71" s="38"/>
-      <c r="E71" s="38"/>
-      <c r="F71" s="39"/>
-      <c r="G71" s="37"/>
-      <c r="H71" s="38"/>
-      <c r="I71" s="38"/>
-      <c r="J71" s="40"/>
-    </row>
-    <row r="72" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C71" s="33"/>
+      <c r="D71" s="34"/>
+      <c r="E71" s="34"/>
+      <c r="F71" s="35"/>
+      <c r="G71" s="33"/>
+      <c r="H71" s="34"/>
+      <c r="I71" s="34"/>
+      <c r="J71" s="36"/>
+    </row>
+    <row r="72" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="31"/>
       <c r="B72" s="29"/>
-      <c r="C72" s="37"/>
-      <c r="D72" s="38"/>
-      <c r="E72" s="38"/>
-      <c r="F72" s="39"/>
-      <c r="G72" s="37"/>
-      <c r="H72" s="38"/>
-      <c r="I72" s="38"/>
-      <c r="J72" s="40"/>
-    </row>
-    <row r="73" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C72" s="33"/>
+      <c r="D72" s="34"/>
+      <c r="E72" s="34"/>
+      <c r="F72" s="35"/>
+      <c r="G72" s="33"/>
+      <c r="H72" s="34"/>
+      <c r="I72" s="34"/>
+      <c r="J72" s="36"/>
+    </row>
+    <row r="73" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="31"/>
       <c r="B73" s="29"/>
-      <c r="C73" s="37"/>
-      <c r="D73" s="38"/>
-      <c r="E73" s="38"/>
-      <c r="F73" s="39"/>
-      <c r="G73" s="37"/>
-      <c r="H73" s="38"/>
-      <c r="I73" s="38"/>
-      <c r="J73" s="40"/>
-    </row>
-    <row r="74" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C73" s="33"/>
+      <c r="D73" s="34"/>
+      <c r="E73" s="34"/>
+      <c r="F73" s="35"/>
+      <c r="G73" s="33"/>
+      <c r="H73" s="34"/>
+      <c r="I73" s="34"/>
+      <c r="J73" s="36"/>
+    </row>
+    <row r="74" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="31"/>
       <c r="B74" s="29"/>
-      <c r="C74" s="37"/>
-      <c r="D74" s="38"/>
-      <c r="E74" s="38"/>
-      <c r="F74" s="39"/>
-      <c r="G74" s="37"/>
-      <c r="H74" s="38"/>
-      <c r="I74" s="38"/>
-      <c r="J74" s="40"/>
-    </row>
-    <row r="75" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C74" s="33"/>
+      <c r="D74" s="34"/>
+      <c r="E74" s="34"/>
+      <c r="F74" s="35"/>
+      <c r="G74" s="33"/>
+      <c r="H74" s="34"/>
+      <c r="I74" s="34"/>
+      <c r="J74" s="36"/>
+    </row>
+    <row r="75" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="31"/>
       <c r="B75" s="29"/>
-      <c r="C75" s="37"/>
-      <c r="D75" s="38"/>
-      <c r="E75" s="38"/>
-      <c r="F75" s="39"/>
-      <c r="G75" s="37"/>
-      <c r="H75" s="38"/>
-      <c r="I75" s="38"/>
-      <c r="J75" s="40"/>
-    </row>
-    <row r="76" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C75" s="33"/>
+      <c r="D75" s="34"/>
+      <c r="E75" s="34"/>
+      <c r="F75" s="35"/>
+      <c r="G75" s="33"/>
+      <c r="H75" s="34"/>
+      <c r="I75" s="34"/>
+      <c r="J75" s="36"/>
+    </row>
+    <row r="76" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="31"/>
       <c r="B76" s="29"/>
-      <c r="C76" s="37"/>
-      <c r="D76" s="38"/>
-      <c r="E76" s="38"/>
-      <c r="F76" s="39"/>
-      <c r="G76" s="37"/>
-      <c r="H76" s="38"/>
-      <c r="I76" s="38"/>
-      <c r="J76" s="40"/>
-    </row>
-    <row r="77" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C76" s="33"/>
+      <c r="D76" s="34"/>
+      <c r="E76" s="34"/>
+      <c r="F76" s="35"/>
+      <c r="G76" s="33"/>
+      <c r="H76" s="34"/>
+      <c r="I76" s="34"/>
+      <c r="J76" s="36"/>
+    </row>
+    <row r="77" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="31"/>
       <c r="B77" s="29"/>
-      <c r="C77" s="37"/>
-      <c r="D77" s="38"/>
-      <c r="E77" s="38"/>
-      <c r="F77" s="39"/>
-      <c r="G77" s="37"/>
-      <c r="H77" s="38"/>
-      <c r="I77" s="38"/>
-      <c r="J77" s="40"/>
-    </row>
-    <row r="78" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C77" s="33"/>
+      <c r="D77" s="34"/>
+      <c r="E77" s="34"/>
+      <c r="F77" s="35"/>
+      <c r="G77" s="33"/>
+      <c r="H77" s="34"/>
+      <c r="I77" s="34"/>
+      <c r="J77" s="36"/>
+    </row>
+    <row r="78" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="31"/>
       <c r="B78" s="29"/>
-      <c r="C78" s="37"/>
-      <c r="D78" s="38"/>
-      <c r="E78" s="38"/>
-      <c r="F78" s="39"/>
-      <c r="G78" s="37"/>
-      <c r="H78" s="38"/>
-      <c r="I78" s="38"/>
-      <c r="J78" s="40"/>
-    </row>
-    <row r="79" spans="1:10" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C78" s="33"/>
+      <c r="D78" s="34"/>
+      <c r="E78" s="34"/>
+      <c r="F78" s="35"/>
+      <c r="G78" s="33"/>
+      <c r="H78" s="34"/>
+      <c r="I78" s="34"/>
+      <c r="J78" s="36"/>
+    </row>
+    <row r="79" spans="1:10" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A79" s="32"/>
       <c r="B79" s="30"/>
-      <c r="C79" s="33"/>
-      <c r="D79" s="34"/>
-      <c r="E79" s="34"/>
-      <c r="F79" s="35"/>
-      <c r="G79" s="33"/>
-      <c r="H79" s="34"/>
-      <c r="I79" s="34"/>
-      <c r="J79" s="36"/>
-    </row>
-    <row r="80" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C79" s="43"/>
+      <c r="D79" s="44"/>
+      <c r="E79" s="44"/>
+      <c r="F79" s="59"/>
+      <c r="G79" s="43"/>
+      <c r="H79" s="44"/>
+      <c r="I79" s="44"/>
+      <c r="J79" s="45"/>
+    </row>
+    <row r="80" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="3" t="s">
         <v>9</v>
       </c>
@@ -2718,6 +2718,102 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="szR9ICFVow2M5dQGXC9LpDgFloQBFwP2+mShiFsOKIbtek3fombW7RZdqbMuVCaQyDvHXBZSvqaXlGO1nxM0Sg==" saltValue="DuPRiT0vUemYjrQ8L06ePw==" spinCount="100000" sheet="1"/>
   <mergeCells count="120">
+    <mergeCell ref="C65:F65"/>
+    <mergeCell ref="G65:J65"/>
+    <mergeCell ref="B38:J38"/>
+    <mergeCell ref="B39:I39"/>
+    <mergeCell ref="B40:I40"/>
+    <mergeCell ref="B42:I42"/>
+    <mergeCell ref="G54:J54"/>
+    <mergeCell ref="C60:F60"/>
+    <mergeCell ref="C79:F79"/>
+    <mergeCell ref="G79:J79"/>
+    <mergeCell ref="C75:F75"/>
+    <mergeCell ref="G75:J75"/>
+    <mergeCell ref="C74:F74"/>
+    <mergeCell ref="G74:J74"/>
+    <mergeCell ref="C76:F76"/>
+    <mergeCell ref="G76:J76"/>
+    <mergeCell ref="C77:F77"/>
+    <mergeCell ref="G77:J77"/>
+    <mergeCell ref="C78:F78"/>
+    <mergeCell ref="G78:J78"/>
+    <mergeCell ref="C71:F71"/>
+    <mergeCell ref="C72:F72"/>
+    <mergeCell ref="C63:F63"/>
+    <mergeCell ref="C69:F69"/>
+    <mergeCell ref="C70:F70"/>
+    <mergeCell ref="C73:F73"/>
+    <mergeCell ref="G73:J73"/>
+    <mergeCell ref="G69:J69"/>
+    <mergeCell ref="G70:J70"/>
+    <mergeCell ref="G71:J71"/>
+    <mergeCell ref="G72:J72"/>
+    <mergeCell ref="C68:F68"/>
+    <mergeCell ref="G68:J68"/>
+    <mergeCell ref="C61:F61"/>
+    <mergeCell ref="G61:J61"/>
+    <mergeCell ref="C62:F62"/>
+    <mergeCell ref="G62:J62"/>
+    <mergeCell ref="C57:F57"/>
+    <mergeCell ref="G57:J57"/>
+    <mergeCell ref="C58:F58"/>
+    <mergeCell ref="C54:F54"/>
+    <mergeCell ref="C16:F16"/>
+    <mergeCell ref="G16:J16"/>
+    <mergeCell ref="C17:F17"/>
+    <mergeCell ref="G17:J17"/>
+    <mergeCell ref="C18:F18"/>
+    <mergeCell ref="G18:J18"/>
+    <mergeCell ref="C22:F22"/>
+    <mergeCell ref="G22:J22"/>
+    <mergeCell ref="C23:F23"/>
+    <mergeCell ref="G23:J23"/>
+    <mergeCell ref="C19:F19"/>
+    <mergeCell ref="G19:J19"/>
+    <mergeCell ref="C20:F20"/>
+    <mergeCell ref="G20:J20"/>
+    <mergeCell ref="G24:J24"/>
+    <mergeCell ref="G33:J33"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A48:J48"/>
+    <mergeCell ref="A5:J5"/>
+    <mergeCell ref="A7:J7"/>
+    <mergeCell ref="C11:J11"/>
+    <mergeCell ref="C12:J12"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="E9:J9"/>
+    <mergeCell ref="G60:J60"/>
+    <mergeCell ref="C34:F34"/>
+    <mergeCell ref="C25:F25"/>
+    <mergeCell ref="G25:J25"/>
+    <mergeCell ref="C31:F31"/>
+    <mergeCell ref="C26:F26"/>
+    <mergeCell ref="G26:J26"/>
+    <mergeCell ref="C27:F27"/>
+    <mergeCell ref="G27:J27"/>
+    <mergeCell ref="C28:F28"/>
+    <mergeCell ref="G28:J28"/>
+    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="G29:J29"/>
+    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="B52:J52"/>
+    <mergeCell ref="B13:J13"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="C14:J14"/>
+    <mergeCell ref="C15:F15"/>
+    <mergeCell ref="G15:J15"/>
+    <mergeCell ref="C21:F21"/>
+    <mergeCell ref="G21:J21"/>
+    <mergeCell ref="C35:F35"/>
+    <mergeCell ref="G32:J32"/>
+    <mergeCell ref="C30:F30"/>
+    <mergeCell ref="G30:J30"/>
+    <mergeCell ref="G31:J31"/>
+    <mergeCell ref="C32:F32"/>
+    <mergeCell ref="C24:F24"/>
+    <mergeCell ref="A44:B44"/>
     <mergeCell ref="C66:F66"/>
     <mergeCell ref="G66:J66"/>
     <mergeCell ref="C67:F67"/>
@@ -2742,102 +2838,6 @@
     <mergeCell ref="G63:J63"/>
     <mergeCell ref="C64:F64"/>
     <mergeCell ref="G64:J64"/>
-    <mergeCell ref="B52:J52"/>
-    <mergeCell ref="B13:J13"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="C14:J14"/>
-    <mergeCell ref="C15:F15"/>
-    <mergeCell ref="G15:J15"/>
-    <mergeCell ref="C21:F21"/>
-    <mergeCell ref="G21:J21"/>
-    <mergeCell ref="C35:F35"/>
-    <mergeCell ref="G32:J32"/>
-    <mergeCell ref="C30:F30"/>
-    <mergeCell ref="G30:J30"/>
-    <mergeCell ref="G31:J31"/>
-    <mergeCell ref="C32:F32"/>
-    <mergeCell ref="C24:F24"/>
-    <mergeCell ref="A44:B44"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A48:J48"/>
-    <mergeCell ref="A5:J5"/>
-    <mergeCell ref="A7:J7"/>
-    <mergeCell ref="C11:J11"/>
-    <mergeCell ref="C12:J12"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="E9:J9"/>
-    <mergeCell ref="G60:J60"/>
-    <mergeCell ref="C61:F61"/>
-    <mergeCell ref="G61:J61"/>
-    <mergeCell ref="C62:F62"/>
-    <mergeCell ref="G62:J62"/>
-    <mergeCell ref="C57:F57"/>
-    <mergeCell ref="G57:J57"/>
-    <mergeCell ref="C58:F58"/>
-    <mergeCell ref="C54:F54"/>
-    <mergeCell ref="C16:F16"/>
-    <mergeCell ref="G16:J16"/>
-    <mergeCell ref="C17:F17"/>
-    <mergeCell ref="G17:J17"/>
-    <mergeCell ref="C18:F18"/>
-    <mergeCell ref="G18:J18"/>
-    <mergeCell ref="C22:F22"/>
-    <mergeCell ref="G22:J22"/>
-    <mergeCell ref="C23:F23"/>
-    <mergeCell ref="G23:J23"/>
-    <mergeCell ref="C19:F19"/>
-    <mergeCell ref="G19:J19"/>
-    <mergeCell ref="C20:F20"/>
-    <mergeCell ref="G20:J20"/>
-    <mergeCell ref="G24:J24"/>
-    <mergeCell ref="G33:J33"/>
-    <mergeCell ref="C34:F34"/>
-    <mergeCell ref="C25:F25"/>
-    <mergeCell ref="G25:J25"/>
-    <mergeCell ref="C31:F31"/>
-    <mergeCell ref="C69:F69"/>
-    <mergeCell ref="C70:F70"/>
-    <mergeCell ref="C73:F73"/>
-    <mergeCell ref="G73:J73"/>
-    <mergeCell ref="G69:J69"/>
-    <mergeCell ref="G70:J70"/>
-    <mergeCell ref="G71:J71"/>
-    <mergeCell ref="G72:J72"/>
-    <mergeCell ref="C68:F68"/>
-    <mergeCell ref="G68:J68"/>
-    <mergeCell ref="C65:F65"/>
-    <mergeCell ref="G65:J65"/>
-    <mergeCell ref="B38:J38"/>
-    <mergeCell ref="B39:I39"/>
-    <mergeCell ref="B40:I40"/>
-    <mergeCell ref="B42:I42"/>
-    <mergeCell ref="G54:J54"/>
-    <mergeCell ref="C60:F60"/>
-    <mergeCell ref="C79:F79"/>
-    <mergeCell ref="G79:J79"/>
-    <mergeCell ref="C26:F26"/>
-    <mergeCell ref="G26:J26"/>
-    <mergeCell ref="C27:F27"/>
-    <mergeCell ref="G27:J27"/>
-    <mergeCell ref="C28:F28"/>
-    <mergeCell ref="G28:J28"/>
-    <mergeCell ref="C29:F29"/>
-    <mergeCell ref="G29:J29"/>
-    <mergeCell ref="C75:F75"/>
-    <mergeCell ref="G75:J75"/>
-    <mergeCell ref="C74:F74"/>
-    <mergeCell ref="G74:J74"/>
-    <mergeCell ref="C76:F76"/>
-    <mergeCell ref="G76:J76"/>
-    <mergeCell ref="C77:F77"/>
-    <mergeCell ref="G77:J77"/>
-    <mergeCell ref="C78:F78"/>
-    <mergeCell ref="G78:J78"/>
-    <mergeCell ref="C33:F33"/>
-    <mergeCell ref="C71:F71"/>
-    <mergeCell ref="C72:F72"/>
-    <mergeCell ref="C63:F63"/>
   </mergeCells>
   <phoneticPr fontId="5"/>
   <dataValidations count="2">
@@ -2861,6 +2861,33 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="263dbbe5-076b-4606-a03b-9598f5f2f35a" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="2bc05441-ecb8-41d0-9872-2862fef3ebb0">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <Owner xmlns="2bc05441-ecb8-41d0-9872-2862fef3ebb0">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </Owner>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x0101004F04D70F81502745934EEFA6067428B0" ma:contentTypeVersion="13" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="e4b1285e22ba7abc44906dbb08eaf091">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="2bc05441-ecb8-41d0-9872-2862fef3ebb0" xmlns:ns3="263dbbe5-076b-4606-a03b-9598f5f2f35a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="f178929248ea575f95a3ed45aedf7b59" ns2:_="" ns3:_="">
     <xsd:import namespace="2bc05441-ecb8-41d0-9872-2862fef3ebb0"/>
@@ -3081,34 +3108,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{548FF6DF-2D3A-4ED2-8121-E02E1A446E35}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="263dbbe5-076b-4606-a03b-9598f5f2f35a"/>
+    <ds:schemaRef ds:uri="2bc05441-ecb8-41d0-9872-2862fef3ebb0"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="263dbbe5-076b-4606-a03b-9598f5f2f35a" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="2bc05441-ecb8-41d0-9872-2862fef3ebb0">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <Owner xmlns="2bc05441-ecb8-41d0-9872-2862fef3ebb0">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </Owner>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{723D2F0B-107C-402F-8FD2-3C816D112A44}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{158E4865-CA9A-4E0D-93F1-B11E919AE0C8}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3125,23 +3144,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{723D2F0B-107C-402F-8FD2-3C816D112A44}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{548FF6DF-2D3A-4ED2-8121-E02E1A446E35}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="263dbbe5-076b-4606-a03b-9598f5f2f35a"/>
-    <ds:schemaRef ds:uri="2bc05441-ecb8-41d0-9872-2862fef3ebb0"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>